--- a/apps_nicolo/LogicCircuits_4s_5r_MAK_REINFORCE/LogicCircuits_4s_5r_MAK_REINFORCE.xlsx
+++ b/apps_nicolo/LogicCircuits_4s_5r_MAK_REINFORCE/LogicCircuits_4s_5r_MAK_REINFORCE.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="48">
   <si>
     <t>Timestamp</t>
   </si>
@@ -100,6 +100,9 @@
     <t>https://www.comet.com/redsnic/logiccircuits-4s-5r-mak-reinforce/db2cbf1518b54eadad99a49ea4cd71e6</t>
   </si>
   <si>
+    <t>NO</t>
+  </si>
+  <si>
     <t>(5, 4, 1, 1280)</t>
   </si>
   <si>
@@ -151,10 +154,7 @@
     <t>https://www.comet.com/redsnic/logiccircuits-4s-5r-mak-reinforce/c30e1e04bdb049fcb16317f8b6967718</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First successful run, I had to lowe the entropy and to increase the risk and weight on the struc entropy. Very good  </t>
+    <t/>
   </si>
   <si>
     <t>(5, 5, 1, 1280)</t>
@@ -168,7 +168,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +179,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -210,13 +216,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -227,16 +230,22 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -544,31 +553,31 @@
   <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="21.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="7" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="21.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="7.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="32.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="15.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="9" width="10.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="17.005" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="9" width="10.005" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="9" width="10.005" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="9" width="17.005" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="9" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="7" width="178.005" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="7" width="75.005" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="178.005" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="8" width="75.005" customWidth="1" bestFit="1"/>
     <col min="16" max="16" style="9" width="17.005" customWidth="1" bestFit="1"/>
     <col min="17" max="17" style="9" width="10.005" customWidth="1" bestFit="1"/>
     <col min="18" max="18" style="9" width="17.005" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="9" width="14.005" customWidth="1" bestFit="1"/>
     <col min="20" max="20" style="9" width="22.005" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="9" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="7" width="26.005" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="7" width="80.005" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="7" width="135.005" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="7" width="19.005" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="8" width="26.005" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="8" width="80.005" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="8" width="135.005" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="8" width="19.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -578,7 +587,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -590,25 +599,25 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -617,22 +626,22 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
@@ -655,419 +664,429 @@
       <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>300</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="5">
+        <v>28</v>
+      </c>
+      <c r="J2" s="6">
         <v>5</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="6">
         <v>1024</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="6">
         <v>10240</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="6">
         <v>128</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="5">
+        <v>30</v>
+      </c>
+      <c r="P2" s="6">
         <v>10</v>
       </c>
-      <c r="Q2" s="5">
-        <v>30</v>
-      </c>
-      <c r="R2" s="5">
+      <c r="Q2" s="6">
+        <v>30</v>
+      </c>
+      <c r="R2" s="6">
         <v>100</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="6">
         <v>1000</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="6">
         <v>1</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="6">
         <v>16</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="1"/>
+        <v>36</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>300</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="5">
+        <v>28</v>
+      </c>
+      <c r="J3" s="6">
         <v>5</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="6">
         <v>1024</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="6">
         <v>10240</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="6">
         <v>128</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="5">
+        <v>30</v>
+      </c>
+      <c r="P3" s="6">
         <v>10</v>
       </c>
-      <c r="Q3" s="5">
-        <v>30</v>
-      </c>
-      <c r="R3" s="5">
+      <c r="Q3" s="6">
+        <v>30</v>
+      </c>
+      <c r="R3" s="6">
         <v>100</v>
       </c>
-      <c r="S3" s="5">
+      <c r="S3" s="6">
         <v>1000</v>
       </c>
-      <c r="T3" s="5">
+      <c r="T3" s="6">
         <v>1</v>
       </c>
-      <c r="U3" s="5">
+      <c r="U3" s="6">
         <v>16</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="1"/>
+        <v>38</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>300</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="5">
+        <v>28</v>
+      </c>
+      <c r="J4" s="6">
         <v>5</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="6">
         <v>1024</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="6">
         <v>10240</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="6">
         <v>128</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" s="5">
+        <v>30</v>
+      </c>
+      <c r="P4" s="6">
         <v>10</v>
       </c>
-      <c r="Q4" s="5">
-        <v>30</v>
-      </c>
-      <c r="R4" s="5">
+      <c r="Q4" s="6">
+        <v>30</v>
+      </c>
+      <c r="R4" s="6">
         <v>100</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="6">
         <v>1000</v>
       </c>
-      <c r="T4" s="5">
+      <c r="T4" s="6">
         <v>1</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U4" s="6">
         <v>16</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>300</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="5">
+        <v>28</v>
+      </c>
+      <c r="J5" s="6">
         <v>5</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="6">
         <v>1024</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="6">
         <v>10240</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="6">
         <v>128</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="5">
+        <v>30</v>
+      </c>
+      <c r="P5" s="6">
         <v>10</v>
       </c>
-      <c r="Q5" s="5">
-        <v>30</v>
-      </c>
-      <c r="R5" s="5">
+      <c r="Q5" s="6">
+        <v>30</v>
+      </c>
+      <c r="R5" s="6">
         <v>100</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="6">
         <v>1000</v>
       </c>
-      <c r="T5" s="5">
+      <c r="T5" s="6">
         <v>1</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="6">
         <v>16</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>300</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="5">
+        <v>28</v>
+      </c>
+      <c r="J6" s="6">
         <v>5</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="6">
         <v>1024</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="6">
         <v>10240</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="6">
         <v>128</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="5">
+        <v>30</v>
+      </c>
+      <c r="P6" s="6">
         <v>10</v>
       </c>
-      <c r="Q6" s="5">
-        <v>30</v>
-      </c>
-      <c r="R6" s="5">
+      <c r="Q6" s="6">
+        <v>30</v>
+      </c>
+      <c r="R6" s="6">
         <v>100</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="6">
         <v>1000</v>
       </c>
-      <c r="T6" s="5">
+      <c r="T6" s="6">
         <v>1</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="6">
         <v>16</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="6">
-        <v>300</v>
-      </c>
-      <c r="D7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="4">
+      <c r="E7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="5">
         <v>0.0001</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>300</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="6">
         <v>5</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="6">
         <v>1024</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="6">
         <v>10240</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="6">
         <v>128</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P7" s="5">
+        <v>30</v>
+      </c>
+      <c r="P7" s="6">
         <v>10</v>
       </c>
-      <c r="Q7" s="5">
-        <v>30</v>
-      </c>
-      <c r="R7" s="5">
+      <c r="Q7" s="6">
+        <v>30</v>
+      </c>
+      <c r="R7" s="6">
         <v>100</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="6">
         <v>1000</v>
       </c>
-      <c r="T7" s="5">
+      <c r="T7" s="6">
         <v>1</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="6">
         <v>16</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>47</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
